--- a/data/trans_bre/P0901-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P0901-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,88</t>
+          <t>-0,45; 4,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 3,74</t>
+          <t>-2,19; 3,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,72</t>
+          <t>-0,96; 3,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 5,61</t>
+          <t>-2,08; 5,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 229,32</t>
+          <t>-12,4; 250,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 148,97</t>
+          <t>-40,73; 129,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 323,52</t>
+          <t>-35,84; 315,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-74,49; 903,79</t>
+          <t>-73,86; 859,49</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,59</t>
+          <t>2,71; 7,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,72</t>
+          <t>-0,89; 3,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,3</t>
+          <t>-1,12; 4,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 1,02</t>
+          <t>-6,42; 1,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,19; 355,39</t>
+          <t>65,24; 345,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 145,91</t>
+          <t>-23,41; 153,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 139,47</t>
+          <t>-25,34; 129,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,96; 19,91</t>
+          <t>-65,1; 22,38</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,06</t>
+          <t>1,55; 7,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,65</t>
+          <t>2,38; 8,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,63</t>
+          <t>1,78; 7,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 5,62</t>
+          <t>-1,03; 5,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,76; 198,9</t>
+          <t>22,21; 191,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,85; 175,73</t>
+          <t>26,65; 168,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,85; 253,04</t>
+          <t>33,9; 236,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 89,17</t>
+          <t>-9,91; 88,49</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,19</t>
+          <t>3,34; 10,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 10,83</t>
+          <t>2,69; 10,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 6,61</t>
+          <t>-0,23; 6,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 14,96</t>
+          <t>1,29; 13,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,7; 192,53</t>
+          <t>31,83; 184,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,72; 149,8</t>
+          <t>24,03; 150,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 79,95</t>
+          <t>-1,92; 79,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,19; 314,84</t>
+          <t>7,86; 278,61</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 8,22</t>
+          <t>-2,67; 8,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 18,85</t>
+          <t>7,4; 18,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 16,68</t>
+          <t>6,27; 16,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 8,41</t>
+          <t>-0,34; 8,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 66,48</t>
+          <t>-15,97; 60,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,9; 135,98</t>
+          <t>38,19; 135,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,27; 154,19</t>
+          <t>38,86; 155,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 48,46</t>
+          <t>-2,13; 44,79</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,4; 21,94</t>
+          <t>8,69; 21,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,35; 20,48</t>
+          <t>5,81; 21,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,96; 25,67</t>
+          <t>12,12; 25,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 13,28</t>
+          <t>-9,4; 13,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,19; 142,33</t>
+          <t>41,28; 144,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,26; 94,4</t>
+          <t>19,78; 96,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,92; 159,94</t>
+          <t>53,67; 163,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,68; 78,64</t>
+          <t>-50,27; 79,37</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 17,56</t>
+          <t>1,12; 18,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,56; 23,05</t>
+          <t>5,41; 22,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,01; 27,34</t>
+          <t>12,19; 28,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,33; 26,31</t>
+          <t>15,08; 26,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 56,59</t>
+          <t>2,81; 57,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,22; 54,69</t>
+          <t>10,08; 55,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,43; 80,57</t>
+          <t>29,09; 85,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,57; 82,82</t>
+          <t>38,46; 84,3</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,74; 8,85</t>
+          <t>5,77; 8,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,66</t>
+          <t>6,92; 10,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,65</t>
+          <t>7,23; 10,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,64; 9,29</t>
+          <t>2,96; 9,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>57,89; 105,6</t>
+          <t>59,29; 107,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,3; 97,22</t>
+          <t>53,74; 96,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,67; 109,19</t>
+          <t>64,43; 107,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,22; 86,49</t>
+          <t>22,56; 88,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P0901-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P0901-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>159,15%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,71</t>
+          <t>-0,25; 4,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,42</t>
+          <t>-1,79; 3,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,5</t>
+          <t>-1,01; 3,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 5,76</t>
+          <t>-0,8; 7,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 250,79</t>
+          <t>-9,19; 246,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 129,14</t>
+          <t>-35,15; 133,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 315,29</t>
+          <t>-40,66; 369,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-73,86; 859,49</t>
+          <t>-49,54; 1425,78</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,48</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-34,51%</t>
+          <t>-23,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,73</t>
+          <t>2,53; 7,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,87</t>
+          <t>-1,03; 3,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,26</t>
+          <t>-1,12; 4,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 1,02</t>
+          <t>-5,33; 1,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,24; 345,04</t>
+          <t>62,84; 343,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 153,47</t>
+          <t>-24,85; 148,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 129,24</t>
+          <t>-18,94; 134,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,1; 22,38</t>
+          <t>-60,01; 40,74</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>42,37%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,18</t>
+          <t>1,35; 6,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,6</t>
+          <t>1,88; 8,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,47</t>
+          <t>2,07; 7,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 5,61</t>
+          <t>0,01; 6,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,21; 191,23</t>
+          <t>20,39; 173,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,65; 168,31</t>
+          <t>21,87; 160,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,9; 236,66</t>
+          <t>33,69; 230,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 88,49</t>
+          <t>-0,27; 105,86</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,05</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,47</t>
+          <t>3,07; 10,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 10,75</t>
+          <t>3,04; 10,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 6,5</t>
+          <t>-0,46; 6,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 13,52</t>
+          <t>-0,75; 6,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,83; 184,27</t>
+          <t>31,02; 186,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,03; 150,09</t>
+          <t>29,87; 153,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 79,06</t>
+          <t>-3,81; 78,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 278,61</t>
+          <t>-4,82; 55,27</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 8,01</t>
+          <t>-3,28; 7,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 18,35</t>
+          <t>7,15; 18,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,27; 16,45</t>
+          <t>5,79; 15,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 8,16</t>
+          <t>1,18; 9,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 60,63</t>
+          <t>-17,23; 57,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,19; 135,4</t>
+          <t>35,55; 138,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,86; 155,89</t>
+          <t>37,74; 151,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 44,79</t>
+          <t>4,99; 52,5</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>12,61</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,69; 21,86</t>
+          <t>9,0; 21,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,81; 21,17</t>
+          <t>5,74; 20,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,12; 25,91</t>
+          <t>11,91; 25,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 13,3</t>
+          <t>7,46; 16,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,28; 144,13</t>
+          <t>39,17; 143,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,78; 96,29</t>
+          <t>18,79; 91,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,67; 163,47</t>
+          <t>55,14; 168,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 79,37</t>
+          <t>37,41; 111,02</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,68</t>
+          <t>21,15</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 18,06</t>
+          <t>0,04; 18,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 22,99</t>
+          <t>6,24; 23,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,19; 28,17</t>
+          <t>11,83; 27,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,08; 26,21</t>
+          <t>14,91; 26,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 57,35</t>
+          <t>0,3; 60,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,08; 55,38</t>
+          <t>11,57; 57,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,09; 85,7</t>
+          <t>26,66; 81,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,46; 84,3</t>
+          <t>37,62; 85,45</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,97</t>
+          <t>5,71; 9,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,92; 10,64</t>
+          <t>7,03; 10,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,61</t>
+          <t>7,12; 10,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,35</t>
+          <t>5,47; 8,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>59,29; 107,94</t>
+          <t>58,13; 109,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,74; 96,58</t>
+          <t>53,85; 94,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,43; 107,94</t>
+          <t>64,83; 110,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,56; 88,01</t>
+          <t>37,97; 68,44</t>
         </is>
       </c>
     </row>
